--- a/NOVEMBER/NOVEMBER FLOOR.xlsx
+++ b/NOVEMBER/NOVEMBER FLOOR.xlsx
@@ -11,7 +11,8 @@
     <sheet name="UD Abdi Jaya (Bag, Cup, Box)" sheetId="2" r:id="rId2"/>
     <sheet name="PT. SUPARMA JAYA TBK (Tissue)" sheetId="3" r:id="rId3"/>
     <sheet name="Vickel Laundry" sheetId="5" r:id="rId4"/>
-    <sheet name="TOTAL" sheetId="4" r:id="rId5"/>
+    <sheet name="Dishy Soap" sheetId="6" r:id="rId5"/>
+    <sheet name="TOTAL" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -110,11 +111,89 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_F7DC5EE9B65A404093E9DC7106EA17B4" descr="WhatsApp Image 2025-11-22 at 11.19.21_b2d71f47"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:srcRect t="10529" b="15447"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7354570" y="6490335"/>
+          <a:ext cx="3192145" cy="4107815"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="ID_65B137B176664CF88877812A0DB613B1" descr="WhatsApp Image 2025-11-24 at 18.54.44_1c844742"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:srcRect l="842" t="17045" r="2783" b="4116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6950710" y="-20955"/>
+          <a:ext cx="2959735" cy="4260215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_0EC8FE7F2FDE486BA9DB2B935A916937" descr="WhatsApp Image 2025-11-25 at 10.50.39_ab457d84"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:srcRect l="1551" t="17216" b="12348"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7005320" y="9714865"/>
+          <a:ext cx="3377565" cy="4250055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="33">
   <si>
     <t>DATE</t>
   </si>
@@ -149,6 +228,21 @@
     <t>P KILAT 2</t>
   </si>
   <si>
+    <t>HAND GLOVES (L)</t>
+  </si>
+  <si>
+    <t>P KILAT 32</t>
+  </si>
+  <si>
+    <t>PAPER BAG L CB08</t>
+  </si>
+  <si>
+    <t>PAPER BAG S CB07</t>
+  </si>
+  <si>
+    <t>BURGER BOX XL</t>
+  </si>
+  <si>
     <t>SO05LC2511000989/00</t>
   </si>
   <si>
@@ -167,6 +261,15 @@
     <t>STATUS</t>
   </si>
   <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>FLOOR CLEANER</t>
+  </si>
+  <si>
     <t>NO</t>
   </si>
   <si>
@@ -186,6 +289,9 @@
   </si>
   <si>
     <t>Vickel Laundry</t>
+  </si>
+  <si>
+    <t>Dishy Soap</t>
   </si>
 </sst>
 </file>
@@ -198,15 +304,36 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="180" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="181" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="179" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="180" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="181" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="182" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="183" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??.00_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="33">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -647,7 +774,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -684,14 +811,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -705,6 +832,35 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -728,9 +884,7 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -741,7 +895,20 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -764,17 +931,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -893,227 +1049,310 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1126,7 +1365,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1135,183 +1374,225 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1636,233 +1917,233 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4285714285714" style="61"/>
-    <col min="2" max="2" width="13.4285714285714" style="61" customWidth="1"/>
-    <col min="3" max="3" width="36" style="61" customWidth="1"/>
-    <col min="4" max="4" width="21.2857142857143" style="62" customWidth="1"/>
-    <col min="5" max="5" width="33.2857142857143" style="61" customWidth="1"/>
-    <col min="6" max="6" width="17.2857142857143" style="61" customWidth="1"/>
-    <col min="7" max="8" width="20.8571428571429" style="61" customWidth="1"/>
-    <col min="9" max="9" width="12.8571428571429" style="61"/>
-    <col min="10" max="10" width="9.14285714285714" style="61"/>
-    <col min="11" max="16384" width="18.0380952380952" style="61"/>
+    <col min="1" max="1" width="17.4285714285714" style="90"/>
+    <col min="2" max="2" width="13.4285714285714" style="90" customWidth="1"/>
+    <col min="3" max="3" width="36" style="90" customWidth="1"/>
+    <col min="4" max="4" width="21.2857142857143" style="88" customWidth="1"/>
+    <col min="5" max="5" width="33.2857142857143" style="90" customWidth="1"/>
+    <col min="6" max="6" width="17.2857142857143" style="90" customWidth="1"/>
+    <col min="7" max="8" width="20.8571428571429" style="90" customWidth="1"/>
+    <col min="9" max="9" width="12.8571428571429" style="90"/>
+    <col min="10" max="10" width="9.14285714285714" style="90"/>
+    <col min="11" max="16384" width="18.0380952380952" style="90"/>
   </cols>
   <sheetData>
-    <row r="1" s="60" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="81" t="s">
+    <row r="1" s="87" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="82" t="s">
+      <c r="F1" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="82" t="s">
+      <c r="G1" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="82" t="s">
+      <c r="H1" s="126" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A2" s="83"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="72">
+    <row r="2" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A2" s="101"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="100">
         <f t="shared" ref="G2:G14" si="0">SUM(D2*F2)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="72">
+      <c r="H2" s="100">
         <f>SUM(G2:G9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A3" s="86"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="72">
+    <row r="3" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A3" s="129"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H3" s="88"/>
-    </row>
-    <row r="4" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A4" s="86"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="72">
+      <c r="H3" s="131"/>
+    </row>
+    <row r="4" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A4" s="129"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="88"/>
-    </row>
-    <row r="5" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A5" s="86"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="72">
+      <c r="H4" s="131"/>
+    </row>
+    <row r="5" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A5" s="129"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" s="88"/>
-    </row>
-    <row r="6" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A6" s="86"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="72">
+      <c r="H5" s="131"/>
+    </row>
+    <row r="6" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A6" s="129"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="88"/>
-    </row>
-    <row r="7" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A7" s="86"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="72">
+      <c r="H6" s="131"/>
+    </row>
+    <row r="7" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A7" s="129"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="88"/>
-    </row>
-    <row r="8" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A8" s="86"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="72">
+      <c r="H7" s="131"/>
+    </row>
+    <row r="8" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A8" s="129"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="88"/>
-    </row>
-    <row r="9" s="60" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A9" s="86"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="72">
+      <c r="H8" s="131"/>
+    </row>
+    <row r="9" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+      <c r="A9" s="129"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="88"/>
-    </row>
-    <row r="10" s="60" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A10" s="83"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72">
+      <c r="H9" s="131"/>
+    </row>
+    <row r="10" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A10" s="101"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="72">
+      <c r="H10" s="100">
         <f>SUM(G10:G13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="60" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A11" s="86"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="72">
+    <row r="11" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A11" s="129"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="88"/>
-    </row>
-    <row r="12" s="60" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A12" s="86"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="72">
+      <c r="H11" s="131"/>
+    </row>
+    <row r="12" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A12" s="129"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="88"/>
-    </row>
-    <row r="13" s="60" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A13" s="86"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="72">
+      <c r="H12" s="131"/>
+    </row>
+    <row r="13" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A13" s="129"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="88"/>
-    </row>
-    <row r="14" s="60" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="69">
+      <c r="H13" s="131"/>
+    </row>
+    <row r="14" s="87" customFormat="1" ht="258" customHeight="1" spans="1:8">
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="69">
+      <c r="H14" s="97">
         <f>SUM(G14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="60" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A15" s="97" t="s">
+    <row r="15" s="87" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="A15" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="103">
+      <c r="B15" s="139"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="144">
         <f>SUM(H2:H14)</f>
         <v>0</v>
       </c>
@@ -1887,163 +2168,253 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.8571428571429" style="61"/>
-    <col min="2" max="2" width="18.8571428571429" style="61" customWidth="1"/>
-    <col min="3" max="3" width="43.0380952380952" style="61" customWidth="1"/>
-    <col min="4" max="4" width="14.4285714285714" style="62" customWidth="1"/>
-    <col min="5" max="5" width="58.9619047619048" style="61" customWidth="1"/>
-    <col min="6" max="6" width="19.5238095238095" style="61" customWidth="1"/>
-    <col min="7" max="8" width="20.8571428571429" style="61" customWidth="1"/>
-    <col min="9" max="9" width="12.8571428571429" style="61"/>
-    <col min="10" max="16384" width="9.14285714285714" style="61"/>
+    <col min="1" max="1" width="19.8571428571429" style="88"/>
+    <col min="2" max="2" width="18.8571428571429" style="88" customWidth="1"/>
+    <col min="3" max="3" width="43.0380952380952" style="89" customWidth="1"/>
+    <col min="4" max="4" width="14.4285714285714" style="88" customWidth="1"/>
+    <col min="5" max="5" width="58.9619047619048" style="90" customWidth="1"/>
+    <col min="6" max="6" width="19.5238095238095" style="90" customWidth="1"/>
+    <col min="7" max="8" width="20.8571428571429" style="90" customWidth="1"/>
+    <col min="9" max="9" width="12.8571428571429" style="90"/>
+    <col min="10" max="16384" width="9.14285714285714" style="90"/>
   </cols>
   <sheetData>
-    <row r="1" s="60" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="63" t="s">
+    <row r="1" s="87" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="H1" s="92" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="60" customFormat="1" ht="249.35" spans="1:8">
-      <c r="A2" s="65">
+    <row r="2" s="87" customFormat="1" ht="249.35" spans="1:8">
+      <c r="A2" s="93">
         <v>45975</v>
       </c>
-      <c r="B2" s="66">
+      <c r="B2" s="94">
         <v>221</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="67">
+      <c r="D2" s="95">
         <v>3</v>
       </c>
-      <c r="E2" s="68" t="str">
+      <c r="E2" s="96" t="str">
         <f>_xlfn.DISPIMG("ID_77CE357CEE334F6D961BD6780F917C7B",1)</f>
         <v>=DISPIMG("ID_77CE357CEE334F6D961BD6780F917C7B",1)</v>
       </c>
-      <c r="F2" s="69">
+      <c r="F2" s="97">
         <v>55000</v>
       </c>
-      <c r="G2" s="70">
+      <c r="G2" s="98">
         <f>D2*F2</f>
         <v>165000</v>
       </c>
-      <c r="H2" s="69">
+      <c r="H2" s="97">
         <f>SUM(G2:G2)</f>
         <v>165000</v>
       </c>
     </row>
-    <row r="3" s="60" customFormat="1" ht="251.35" spans="1:8">
-      <c r="A3" s="65">
+    <row r="3" s="87" customFormat="1" ht="251.35" spans="1:8">
+      <c r="A3" s="93">
         <v>45976</v>
       </c>
-      <c r="B3" s="66">
+      <c r="B3" s="94">
         <v>254</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="67">
+      <c r="D3" s="95">
         <v>5</v>
       </c>
-      <c r="E3" s="68" t="str">
+      <c r="E3" s="96" t="str">
         <f>_xlfn.DISPIMG("ID_53A5575CEC60468792705E317509501C",1)</f>
         <v>=DISPIMG("ID_53A5575CEC60468792705E317509501C",1)</v>
       </c>
-      <c r="F3" s="70">
+      <c r="F3" s="98">
         <v>13000</v>
       </c>
-      <c r="G3" s="70">
+      <c r="G3" s="98">
         <f>D3*F3</f>
         <v>65000</v>
       </c>
-      <c r="H3" s="72">
+      <c r="H3" s="100">
         <f>SUM(G3:G3)</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="4" s="60" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A4" s="73"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-    </row>
-    <row r="5" s="60" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A5" s="73"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-    </row>
-    <row r="6" s="60" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A6" s="73"/>
-      <c r="B6" s="74"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-    </row>
-    <row r="7" s="60" customFormat="1" ht="200" customHeight="1" spans="1:8">
-      <c r="A7" s="73"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="69"/>
-    </row>
-    <row r="8" s="60" customFormat="1" spans="1:8">
-      <c r="A8" s="79"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80">
-        <f>SUM(H2:H7)</f>
-        <v>230000</v>
+    <row r="4" s="87" customFormat="1" ht="120" customHeight="1" spans="1:8">
+      <c r="A4" s="101">
+        <v>45982</v>
+      </c>
+      <c r="B4" s="102">
+        <v>471</v>
+      </c>
+      <c r="C4" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="95">
+        <v>3</v>
+      </c>
+      <c r="E4" s="96" t="str">
+        <f>_xlfn.DISPIMG("ID_F7DC5EE9B65A404093E9DC7106EA17B4",1)</f>
+        <v>=DISPIMG("ID_F7DC5EE9B65A404093E9DC7106EA17B4",1)</v>
+      </c>
+      <c r="F4" s="98">
+        <v>55000</v>
+      </c>
+      <c r="G4" s="98">
+        <f>D4*F4</f>
+        <v>165000</v>
+      </c>
+      <c r="H4" s="100">
+        <f>SUM(G4:G5)</f>
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="5" s="87" customFormat="1" ht="120" customHeight="1" spans="1:8">
+      <c r="A5" s="103"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="95">
+        <v>1</v>
+      </c>
+      <c r="E5" s="105"/>
+      <c r="F5" s="98">
+        <v>30000</v>
+      </c>
+      <c r="G5" s="98">
+        <f>D5*F5</f>
+        <v>30000</v>
+      </c>
+      <c r="H5" s="106"/>
+    </row>
+    <row r="6" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A6" s="107">
+        <v>45985</v>
+      </c>
+      <c r="B6" s="108">
+        <v>523</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="95">
+        <v>200</v>
+      </c>
+      <c r="E6" s="109" t="str">
+        <f>_xlfn.DISPIMG("ID_0EC8FE7F2FDE486BA9DB2B935A916937",1)</f>
+        <v>=DISPIMG("ID_0EC8FE7F2FDE486BA9DB2B935A916937",1)</v>
+      </c>
+      <c r="F6" s="98">
+        <v>2300</v>
+      </c>
+      <c r="G6" s="98">
+        <f>D6*F6</f>
+        <v>460000</v>
+      </c>
+      <c r="H6" s="110">
+        <f>SUM(G6:G8)</f>
+        <v>1335000</v>
+      </c>
+    </row>
+    <row r="7" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A7" s="111"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="113">
+        <v>250</v>
+      </c>
+      <c r="E7" s="114"/>
+      <c r="F7" s="115">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="98">
+        <f>D7*F7</f>
+        <v>500000</v>
+      </c>
+      <c r="H7" s="116"/>
+    </row>
+    <row r="8" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A8" s="117"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="99" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="113">
+        <v>150</v>
+      </c>
+      <c r="E8" s="119"/>
+      <c r="F8" s="115">
+        <v>2500</v>
+      </c>
+      <c r="G8" s="98">
+        <f>D8*F8</f>
+        <v>375000</v>
+      </c>
+      <c r="H8" s="120"/>
+    </row>
+    <row r="9" s="87" customFormat="1" ht="200" customHeight="1" spans="1:8">
+      <c r="A9" s="93"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="97"/>
+    </row>
+    <row r="10" s="87" customFormat="1" spans="1:8">
+      <c r="A10" s="123"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124">
+        <f>SUM(H2:H9)</f>
+        <v>1760000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
+  <mergeCells count="9">
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H6:H8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2066,197 +2437,197 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:7">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="51" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A2" s="25">
+      <c r="A2" s="52">
         <v>45968</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="27">
+      <c r="B2" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="54">
         <v>40</v>
       </c>
-      <c r="E2" s="28" t="str">
+      <c r="E2" s="55" t="str">
         <f>_xlfn.DISPIMG("ID_2900A6598AF34EAF8E34FD7992770F9A",1)</f>
         <v>=DISPIMG("ID_2900A6598AF34EAF8E34FD7992770F9A",1)</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="56">
         <v>6063.96</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="57">
         <f>SUM(D2*F2)</f>
         <v>242558.4</v>
       </c>
     </row>
     <row r="3" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A3" s="25"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="30"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="57"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="25"/>
-      <c r="B4" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35">
+      <c r="A4" s="52"/>
+      <c r="B4" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62">
         <f>SUM(G2:G3)</f>
         <v>242558.4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="25"/>
-      <c r="B5" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35">
+      <c r="A5" s="52"/>
+      <c r="B5" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="61"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62">
         <f>G4*11%</f>
         <v>26681.424</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36">
+      <c r="A6" s="52"/>
+      <c r="B6" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63">
         <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="25"/>
-      <c r="B7" s="34" t="s">
+      <c r="A7" s="52"/>
+      <c r="B7" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37">
+      <c r="C7" s="61"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64">
         <v>269482</v>
       </c>
     </row>
     <row r="8" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="42"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="69"/>
     </row>
     <row r="9" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A9" s="25"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="42"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="69"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="45"/>
-      <c r="B10" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35">
+      <c r="A10" s="72"/>
+      <c r="B10" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62">
         <f>SUM(G8:G9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="76"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="45"/>
-      <c r="B12" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="63"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51" t="s">
+      <c r="A13" s="77"/>
+      <c r="B13" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="37">
+      <c r="C13" s="79"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="64">
         <f>SUM(G10:G12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="57">
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="84">
         <f>G7+G13</f>
         <v>269482</v>
       </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="59"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2292,254 +2663,254 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" style="8"/>
-    <col min="2" max="2" width="12.6" style="9" customWidth="1"/>
-    <col min="3" max="3" width="38.7142857142857" style="8" customWidth="1"/>
-    <col min="4" max="4" width="18.8285714285714" style="8" customWidth="1"/>
-    <col min="5" max="5" width="12.2857142857143" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9.14285714285714" style="8"/>
+    <col min="1" max="1" width="9.14285714285714" style="12"/>
+    <col min="2" max="2" width="12.6" style="36" customWidth="1"/>
+    <col min="3" max="3" width="38.7142857142857" style="12" customWidth="1"/>
+    <col min="4" max="4" width="18.8285714285714" style="12" customWidth="1"/>
+    <col min="5" max="5" width="12.2857142857143" style="12" customWidth="1"/>
+    <col min="6" max="16384" width="9.14285714285714" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" ht="19" customHeight="1" spans="1:5">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="35" customFormat="1" ht="19" customHeight="1" spans="1:5">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="14"/>
-    </row>
-    <row r="3" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="4" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17"/>
-    </row>
-    <row r="6" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-    </row>
-    <row r="7" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
-    </row>
-    <row r="8" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17"/>
-    </row>
-    <row r="9" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17"/>
-    </row>
-    <row r="10" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
-    </row>
-    <row r="12" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-    </row>
-    <row r="14" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
-    </row>
-    <row r="17" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-    </row>
-    <row r="18" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-    </row>
-    <row r="19" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17"/>
-    </row>
-    <row r="21" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-    </row>
-    <row r="22" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
-    </row>
-    <row r="23" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
-    </row>
-    <row r="24" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="14"/>
-    </row>
-    <row r="25" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="14"/>
-    </row>
-    <row r="26" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="14"/>
-    </row>
-    <row r="27" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A27" s="12">
+      <c r="E1" s="37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="41"/>
+    </row>
+    <row r="3" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+    </row>
+    <row r="4" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
+    </row>
+    <row r="5" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A5" s="39"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="44"/>
+    </row>
+    <row r="6" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A6" s="39"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="44"/>
+    </row>
+    <row r="7" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="44"/>
+    </row>
+    <row r="8" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A8" s="39"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="44"/>
+    </row>
+    <row r="9" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A9" s="39"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="44"/>
+    </row>
+    <row r="10" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A10" s="39"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
+    </row>
+    <row r="11" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="44"/>
+    </row>
+    <row r="12" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A12" s="39"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="44"/>
+    </row>
+    <row r="13" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A13" s="39"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44"/>
+    </row>
+    <row r="14" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A14" s="39"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="44"/>
+    </row>
+    <row r="15" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A15" s="39"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="44"/>
+    </row>
+    <row r="16" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A16" s="39"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="44"/>
+    </row>
+    <row r="17" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="44"/>
+    </row>
+    <row r="18" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A18" s="39"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="44"/>
+    </row>
+    <row r="19" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="44"/>
+    </row>
+    <row r="20" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A20" s="39"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="44"/>
+    </row>
+    <row r="21" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+    </row>
+    <row r="22" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A22" s="39"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="44"/>
+    </row>
+    <row r="23" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A23" s="39"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="44"/>
+    </row>
+    <row r="24" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="41"/>
+    </row>
+    <row r="25" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="41"/>
+    </row>
+    <row r="26" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A26" s="39"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="41"/>
+    </row>
+    <row r="27" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A27" s="39">
         <v>45960</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="14"/>
-    </row>
-    <row r="28" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A28" s="12">
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="41"/>
+    </row>
+    <row r="28" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A28" s="39">
         <v>45961</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="14"/>
-    </row>
-    <row r="29" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="14"/>
-    </row>
-    <row r="30" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="14"/>
-    </row>
-    <row r="31" s="8" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="14"/>
-    </row>
-    <row r="32" s="8" customFormat="1" spans="1:5">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="20">
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="41"/>
+    </row>
+    <row r="29" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A29" s="39"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="41"/>
+    </row>
+    <row r="30" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="41"/>
+    </row>
+    <row r="31" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
+      <c r="A31" s="39"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="41"/>
+    </row>
+    <row r="32" s="12" customFormat="1" spans="1:5">
+      <c r="A32" s="45"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="47">
         <f>SUM(D2:D31)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="22"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2554,85 +2925,222 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="21.8571428571429" customWidth="1"/>
+    <col min="1" max="1" width="21.1428571428571" style="13" customWidth="1"/>
+    <col min="2" max="2" width="27.5714285714286" style="12" customWidth="1"/>
+    <col min="3" max="3" width="30.752380952381" style="12" customWidth="1"/>
+    <col min="4" max="4" width="65.7047619047619" style="12" customWidth="1"/>
+    <col min="5" max="7" width="32.3333333333333" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.14285714285714" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="11" customFormat="1" ht="35" customHeight="1" spans="1:7">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="12" customFormat="1" ht="240.3" spans="1:7">
+      <c r="A2" s="16">
+        <v>45982</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="18">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="str">
+        <f>_xlfn.DISPIMG("ID_65B137B176664CF88877812A0DB613B1",1)</f>
+        <v>=DISPIMG("ID_65B137B176664CF88877812A0DB613B1",1)</v>
+      </c>
+      <c r="E2" s="20">
+        <v>55000</v>
+      </c>
+      <c r="F2" s="21">
+        <f>C2*E2</f>
+        <v>110000</v>
+      </c>
+      <c r="G2" s="22">
+        <f>SUM(F2:F2)</f>
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="3" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
+    </row>
+    <row r="4" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
+      <c r="A4" s="23"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="30"/>
+    </row>
+    <row r="5" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
+      <c r="A5" s="23"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" s="12" customFormat="1" ht="23.25" spans="1:7">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="32"/>
+    </row>
+    <row r="7" s="12" customFormat="1" ht="39" customHeight="1" spans="1:7">
+      <c r="A7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="34">
+        <f>SUM(G2)</f>
+        <v>110000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="G3:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="9.14285714285714" style="1"/>
+    <col min="2" max="2" width="21.8571428571429" style="2" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
+      <c r="A1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="B2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="8">
         <f>'Anugrah (Bag, Cup, Box)'!H15</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="3">
-        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H8</f>
-        <v>230000</v>
+      <c r="B3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="8">
+        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H10</f>
+        <v>1760000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8">
         <f>'PT. SUPARMA JAYA TBK (Tissue)'!E14</f>
         <v>269482</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="9">
         <f>'Vickel Laundry'!C32</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="9">
+        <f>'Dishy Soap'!G7</f>
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="6">
+      <c r="B7" s="7"/>
+      <c r="C7" s="10">
         <f>SUM(C2:C5)</f>
-        <v>499482</v>
+        <v>2029482</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/NOVEMBER/NOVEMBER FLOOR.xlsx
+++ b/NOVEMBER/NOVEMBER FLOOR.xlsx
@@ -114,39 +114,13 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_F7DC5EE9B65A404093E9DC7106EA17B4" descr="WhatsApp Image 2025-11-22 at 11.19.21_b2d71f47"/>
+        <xdr:cNvPr id="7" name="ID_65B137B176664CF88877812A0DB613B1" descr="WhatsApp Image 2025-11-24 at 18.54.44_1c844742"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId4"/>
-        <a:srcRect t="10529" b="15447"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="7354570" y="6490335"/>
-          <a:ext cx="3192145" cy="4107815"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="ID_65B137B176664CF88877812A0DB613B1" descr="WhatsApp Image 2025-11-24 at 18.54.44_1c844742"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
         <a:srcRect l="842" t="17045" r="2783" b="4116"/>
         <a:stretch>
           <a:fillRect/>
@@ -172,7 +146,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
+        <a:blip r:embed="rId5"/>
         <a:srcRect l="1551" t="17216" b="12348"/>
         <a:stretch>
           <a:fillRect/>
@@ -193,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="31">
   <si>
     <t>DATE</t>
   </si>
@@ -226,12 +200,6 @@
   </si>
   <si>
     <t>P KILAT 2</t>
-  </si>
-  <si>
-    <t>HAND GLOVES (L)</t>
-  </si>
-  <si>
-    <t>P KILAT 32</t>
   </si>
   <si>
     <t>PAPER BAG L CB08</t>
@@ -1179,7 +1147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1429,9 +1397,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1469,6 +1434,21 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1479,51 +1459,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1547,15 +1482,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1563,9 +1489,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1917,233 +1840,233 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4285714285714" style="90"/>
-    <col min="2" max="2" width="13.4285714285714" style="90" customWidth="1"/>
-    <col min="3" max="3" width="36" style="90" customWidth="1"/>
+    <col min="1" max="1" width="17.4285714285714" style="89"/>
+    <col min="2" max="2" width="13.4285714285714" style="89" customWidth="1"/>
+    <col min="3" max="3" width="36" style="89" customWidth="1"/>
     <col min="4" max="4" width="21.2857142857143" style="88" customWidth="1"/>
-    <col min="5" max="5" width="33.2857142857143" style="90" customWidth="1"/>
-    <col min="6" max="6" width="17.2857142857143" style="90" customWidth="1"/>
-    <col min="7" max="8" width="20.8571428571429" style="90" customWidth="1"/>
-    <col min="9" max="9" width="12.8571428571429" style="90"/>
-    <col min="10" max="10" width="9.14285714285714" style="90"/>
-    <col min="11" max="16384" width="18.0380952380952" style="90"/>
+    <col min="5" max="5" width="33.2857142857143" style="89" customWidth="1"/>
+    <col min="6" max="6" width="17.2857142857143" style="89" customWidth="1"/>
+    <col min="7" max="8" width="20.8571428571429" style="89" customWidth="1"/>
+    <col min="9" max="9" width="12.8571428571429" style="89"/>
+    <col min="10" max="10" width="9.14285714285714" style="89"/>
+    <col min="11" max="16384" width="18.0380952380952" style="89"/>
   </cols>
   <sheetData>
     <row r="1" s="87" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126" t="s">
+      <c r="B1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="126" t="s">
+      <c r="C1" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="126" t="s">
+      <c r="D1" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="126" t="s">
+      <c r="E1" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="126" t="s">
+      <c r="F1" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="G1" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="126" t="s">
+      <c r="H1" s="115" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A2" s="101"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="100">
+      <c r="A2" s="100"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="99">
         <f t="shared" ref="G2:G14" si="0">SUM(D2*F2)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="100">
+      <c r="H2" s="99">
         <f>SUM(G2:G9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A3" s="129"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="100">
+      <c r="A3" s="102"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H3" s="131"/>
+      <c r="H3" s="106"/>
     </row>
     <row r="4" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A4" s="129"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="100">
+      <c r="A4" s="102"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="131"/>
+      <c r="H4" s="106"/>
     </row>
     <row r="5" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A5" s="129"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="100">
+      <c r="A5" s="102"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" s="131"/>
+      <c r="H5" s="106"/>
     </row>
     <row r="6" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A6" s="129"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="100">
+      <c r="A6" s="102"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="131"/>
+      <c r="H6" s="106"/>
     </row>
     <row r="7" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A7" s="129"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="100">
+      <c r="A7" s="102"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="131"/>
+      <c r="H7" s="106"/>
     </row>
     <row r="8" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A8" s="129"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="100">
+      <c r="A8" s="102"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="131"/>
+      <c r="H8" s="106"/>
     </row>
     <row r="9" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A9" s="129"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="100">
+      <c r="A9" s="102"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="131"/>
+      <c r="H9" s="106"/>
     </row>
     <row r="10" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A10" s="101"/>
-      <c r="B10" s="102"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="128"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100">
+      <c r="A10" s="100"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="100">
+      <c r="H10" s="99">
         <f>SUM(G10:G13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A11" s="129"/>
-      <c r="B11" s="135"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="100">
+      <c r="A11" s="102"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="131"/>
+      <c r="H11" s="106"/>
     </row>
     <row r="12" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A12" s="129"/>
-      <c r="B12" s="135"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="100">
+      <c r="A12" s="102"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="131"/>
+      <c r="H12" s="106"/>
     </row>
     <row r="13" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A13" s="129"/>
-      <c r="B13" s="135"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="100">
+      <c r="A13" s="102"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="131"/>
+      <c r="H13" s="106"/>
     </row>
     <row r="14" s="87" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="97">
+      <c r="A14" s="92"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="97">
+      <c r="H14" s="96">
         <f>SUM(G14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" s="87" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A15" s="138" t="s">
+      <c r="A15" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="144">
+      <c r="B15" s="124"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="129">
         <f>SUM(H2:H14)</f>
         <v>0</v>
       </c>
@@ -2168,253 +2091,201 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="19.8571428571429" style="88"/>
     <col min="2" max="2" width="18.8571428571429" style="88" customWidth="1"/>
-    <col min="3" max="3" width="43.0380952380952" style="89" customWidth="1"/>
+    <col min="3" max="3" width="43.0380952380952" style="88" customWidth="1"/>
     <col min="4" max="4" width="14.4285714285714" style="88" customWidth="1"/>
-    <col min="5" max="5" width="58.9619047619048" style="90" customWidth="1"/>
-    <col min="6" max="6" width="19.5238095238095" style="90" customWidth="1"/>
-    <col min="7" max="8" width="20.8571428571429" style="90" customWidth="1"/>
-    <col min="9" max="9" width="12.8571428571429" style="90"/>
-    <col min="10" max="16384" width="9.14285714285714" style="90"/>
+    <col min="5" max="5" width="58.9619047619048" style="89" customWidth="1"/>
+    <col min="6" max="6" width="19.5238095238095" style="89" customWidth="1"/>
+    <col min="7" max="8" width="20.8571428571429" style="89" customWidth="1"/>
+    <col min="9" max="9" width="12.8571428571429" style="89"/>
+    <col min="10" max="16384" width="9.14285714285714" style="89"/>
   </cols>
   <sheetData>
     <row r="1" s="87" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="92" t="s">
+      <c r="F1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="92" t="s">
+      <c r="G1" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="92" t="s">
+      <c r="H1" s="91" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" s="87" customFormat="1" ht="249.35" spans="1:8">
-      <c r="A2" s="93">
+      <c r="A2" s="92">
         <v>45975</v>
       </c>
-      <c r="B2" s="94">
+      <c r="B2" s="93">
         <v>221</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="95">
+      <c r="D2" s="94">
         <v>3</v>
       </c>
-      <c r="E2" s="96" t="str">
+      <c r="E2" s="95" t="str">
         <f>_xlfn.DISPIMG("ID_77CE357CEE334F6D961BD6780F917C7B",1)</f>
         <v>=DISPIMG("ID_77CE357CEE334F6D961BD6780F917C7B",1)</v>
       </c>
-      <c r="F2" s="97">
+      <c r="F2" s="96">
         <v>55000</v>
       </c>
-      <c r="G2" s="98">
+      <c r="G2" s="97">
         <f>D2*F2</f>
         <v>165000</v>
       </c>
-      <c r="H2" s="97">
+      <c r="H2" s="96">
         <f>SUM(G2:G2)</f>
         <v>165000</v>
       </c>
     </row>
     <row r="3" s="87" customFormat="1" ht="251.35" spans="1:8">
-      <c r="A3" s="93">
+      <c r="A3" s="92">
         <v>45976</v>
       </c>
-      <c r="B3" s="94">
+      <c r="B3" s="93">
         <v>254</v>
       </c>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="95">
+      <c r="D3" s="94">
         <v>5</v>
       </c>
-      <c r="E3" s="96" t="str">
+      <c r="E3" s="95" t="str">
         <f>_xlfn.DISPIMG("ID_53A5575CEC60468792705E317509501C",1)</f>
         <v>=DISPIMG("ID_53A5575CEC60468792705E317509501C",1)</v>
       </c>
-      <c r="F3" s="98">
+      <c r="F3" s="97">
         <v>13000</v>
       </c>
-      <c r="G3" s="98">
+      <c r="G3" s="97">
         <f>D3*F3</f>
         <v>65000</v>
       </c>
-      <c r="H3" s="100">
+      <c r="H3" s="99">
         <f>SUM(G3:G3)</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="4" s="87" customFormat="1" ht="120" customHeight="1" spans="1:8">
-      <c r="A4" s="101">
-        <v>45982</v>
-      </c>
-      <c r="B4" s="102">
-        <v>471</v>
-      </c>
-      <c r="C4" s="99" t="s">
+    <row r="4" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A4" s="100">
+        <v>45985</v>
+      </c>
+      <c r="B4" s="101">
+        <v>523</v>
+      </c>
+      <c r="C4" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="95">
-        <v>3</v>
-      </c>
-      <c r="E4" s="96" t="str">
-        <f>_xlfn.DISPIMG("ID_F7DC5EE9B65A404093E9DC7106EA17B4",1)</f>
-        <v>=DISPIMG("ID_F7DC5EE9B65A404093E9DC7106EA17B4",1)</v>
-      </c>
-      <c r="F4" s="98">
-        <v>55000</v>
-      </c>
-      <c r="G4" s="98">
-        <f>D4*F4</f>
-        <v>165000</v>
-      </c>
-      <c r="H4" s="100">
-        <f>SUM(G4:G5)</f>
-        <v>195000</v>
-      </c>
-    </row>
-    <row r="5" s="87" customFormat="1" ht="120" customHeight="1" spans="1:8">
-      <c r="A5" s="103"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="95">
-        <v>1</v>
-      </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="98">
-        <v>30000</v>
-      </c>
-      <c r="G5" s="98">
-        <f>D5*F5</f>
-        <v>30000</v>
-      </c>
-      <c r="H5" s="106"/>
-    </row>
-    <row r="6" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A6" s="107">
-        <v>45985</v>
-      </c>
-      <c r="B6" s="108">
-        <v>523</v>
-      </c>
-      <c r="C6" s="99" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="95">
+      <c r="D4" s="94">
         <v>200</v>
       </c>
-      <c r="E6" s="109" t="str">
+      <c r="E4" s="95" t="str">
         <f>_xlfn.DISPIMG("ID_0EC8FE7F2FDE486BA9DB2B935A916937",1)</f>
         <v>=DISPIMG("ID_0EC8FE7F2FDE486BA9DB2B935A916937",1)</v>
       </c>
-      <c r="F6" s="98">
+      <c r="F4" s="97">
         <v>2300</v>
       </c>
-      <c r="G6" s="98">
+      <c r="G4" s="97">
+        <f>D4*F4</f>
+        <v>460000</v>
+      </c>
+      <c r="H4" s="99">
+        <f>SUM(G4:G6)</f>
+        <v>1335000</v>
+      </c>
+    </row>
+    <row r="5" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A5" s="102"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="104">
+        <v>250</v>
+      </c>
+      <c r="E5" s="105"/>
+      <c r="F5" s="99">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="97">
+        <f>D5*F5</f>
+        <v>500000</v>
+      </c>
+      <c r="H5" s="106"/>
+    </row>
+    <row r="6" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A6" s="107"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="104">
+        <v>150</v>
+      </c>
+      <c r="E6" s="109"/>
+      <c r="F6" s="99">
+        <v>2500</v>
+      </c>
+      <c r="G6" s="97">
         <f>D6*F6</f>
-        <v>460000</v>
-      </c>
-      <c r="H6" s="110">
-        <f>SUM(G6:G8)</f>
-        <v>1335000</v>
-      </c>
-    </row>
-    <row r="7" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A7" s="111"/>
-      <c r="B7" s="112"/>
-      <c r="C7" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="113">
-        <v>250</v>
-      </c>
-      <c r="E7" s="114"/>
-      <c r="F7" s="115">
-        <v>2000</v>
-      </c>
-      <c r="G7" s="98">
-        <f>D7*F7</f>
-        <v>500000</v>
-      </c>
-      <c r="H7" s="116"/>
-    </row>
-    <row r="8" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A8" s="117"/>
-      <c r="B8" s="118"/>
-      <c r="C8" s="99" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="113">
-        <v>150</v>
-      </c>
-      <c r="E8" s="119"/>
-      <c r="F8" s="115">
-        <v>2500</v>
-      </c>
-      <c r="G8" s="98">
-        <f>D8*F8</f>
         <v>375000</v>
       </c>
-      <c r="H8" s="120"/>
-    </row>
-    <row r="9" s="87" customFormat="1" ht="200" customHeight="1" spans="1:8">
-      <c r="A9" s="93"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="97"/>
-    </row>
-    <row r="10" s="87" customFormat="1" spans="1:8">
-      <c r="A10" s="123"/>
-      <c r="B10" s="123"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124">
-        <f>SUM(H2:H9)</f>
-        <v>1760000</v>
+      <c r="H6" s="110"/>
+    </row>
+    <row r="7" s="87" customFormat="1" ht="200" customHeight="1" spans="1:8">
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="96"/>
+    </row>
+    <row r="8" s="87" customFormat="1" spans="1:8">
+      <c r="A8" s="112"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113">
+        <f>SUM(H2:H7)</f>
+        <v>1565000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="H6:H8"/>
+  <mergeCells count="5">
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="H4:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2464,10 +2335,10 @@
         <v>45968</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" s="54">
         <v>40</v>
@@ -2496,7 +2367,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="52"/>
       <c r="B4" s="61" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="62"/>
@@ -2510,7 +2381,7 @@
     <row r="5" spans="1:7">
       <c r="A5" s="52"/>
       <c r="B5" s="61" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="62"/>
@@ -2524,7 +2395,7 @@
     <row r="6" spans="1:7">
       <c r="A6" s="52"/>
       <c r="B6" s="61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="61"/>
       <c r="D6" s="62"/>
@@ -2568,7 +2439,7 @@
     <row r="10" spans="1:7">
       <c r="A10" s="72"/>
       <c r="B10" s="61" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="61"/>
       <c r="D10" s="62"/>
@@ -2582,7 +2453,7 @@
     <row r="11" spans="1:7">
       <c r="A11" s="74"/>
       <c r="B11" s="75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="76"/>
       <c r="D11" s="62"/>
@@ -2593,7 +2464,7 @@
     <row r="12" spans="1:7">
       <c r="A12" s="72"/>
       <c r="B12" s="61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="62"/>
@@ -2685,7 +2556,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
@@ -2941,10 +2812,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>4</v>
@@ -2964,7 +2835,7 @@
         <v>45982</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="18">
         <v>2</v>
@@ -3059,13 +2930,13 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3073,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="8">
         <f>'Anugrah (Bag, Cup, Box)'!H15</f>
@@ -3085,11 +2956,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8">
-        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H10</f>
-        <v>1760000</v>
+        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H8</f>
+        <v>1565000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3097,7 +2968,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="8">
         <f>'PT. SUPARMA JAYA TBK (Tissue)'!E14</f>
@@ -3109,7 +2980,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="9">
         <f>'Vickel Laundry'!C32</f>
@@ -3121,7 +2992,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="9">
         <f>'Dishy Soap'!G7</f>
@@ -3135,7 +3006,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="10">
         <f>SUM(C2:C5)</f>
-        <v>2029482</v>
+        <v>1834482</v>
       </c>
     </row>
   </sheetData>

--- a/NOVEMBER/NOVEMBER FLOOR.xlsx
+++ b/NOVEMBER/NOVEMBER FLOOR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -163,11 +163,37 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_1BF8DA62F9C54E9D82DEA162EB6C0D2C" descr="WhatsApp Image 2025-11-27 at 12.24.53_64d6a880"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:srcRect t="14478" r="1369" b="8928"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6172835" y="573405"/>
+          <a:ext cx="2483485" cy="3385185"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
   <si>
     <t>DATE</t>
   </si>
@@ -191,6 +217,18 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>PAPERBAG HANDLE L BROWN</t>
+  </si>
+  <si>
+    <t>PAPERBAG HANDLE S BROWN</t>
+  </si>
+  <si>
+    <t>CUP SAUCE 60 ML</t>
+  </si>
+  <si>
+    <t>PAPER LUNCH BOX L BROWN</t>
   </si>
   <si>
     <t>GRAND TOTAL</t>
@@ -1147,7 +1185,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1480,15 +1518,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1837,7 +1866,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17.4285714285714" style="89"/>
@@ -1848,7 +1877,7 @@
     <col min="6" max="6" width="17.2857142857143" style="89" customWidth="1"/>
     <col min="7" max="8" width="20.8571428571429" style="89" customWidth="1"/>
     <col min="9" max="9" width="12.8571428571429" style="89"/>
-    <col min="10" max="10" width="9.14285714285714" style="89"/>
+    <col min="10" max="10" width="12" style="89"/>
     <col min="11" max="16384" width="18.0380952380952" style="89"/>
   </cols>
   <sheetData>
@@ -1878,210 +1907,189 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A2" s="100"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="96"/>
+    <row r="2" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
+      <c r="A2" s="100">
+        <v>45988</v>
+      </c>
+      <c r="B2" s="93">
+        <v>2377</v>
+      </c>
+      <c r="C2" s="116" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="117">
+        <v>400</v>
+      </c>
+      <c r="E2" s="95" t="str">
+        <f>_xlfn.DISPIMG("ID_1BF8DA62F9C54E9D82DEA162EB6C0D2C",1)</f>
+        <v>=DISPIMG("ID_1BF8DA62F9C54E9D82DEA162EB6C0D2C",1)</v>
+      </c>
+      <c r="F2" s="96">
+        <v>2900</v>
+      </c>
       <c r="G2" s="99">
-        <f t="shared" ref="G2:G14" si="0">SUM(D2*F2)</f>
-        <v>0</v>
+        <f>SUM(D2*F2)</f>
+        <v>1160000</v>
       </c>
       <c r="H2" s="99">
-        <f>SUM(G2:G9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+        <f>SUM(G2:G5)</f>
+        <v>4047600</v>
+      </c>
+    </row>
+    <row r="3" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A3" s="102"/>
       <c r="B3" s="93"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="117"/>
+      <c r="C3" s="116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="117">
+        <v>400</v>
+      </c>
       <c r="E3" s="105"/>
-      <c r="F3" s="96"/>
+      <c r="F3" s="96">
+        <v>2800</v>
+      </c>
       <c r="G3" s="99">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(D3*F3)</f>
+        <v>1120000</v>
       </c>
       <c r="H3" s="106"/>
     </row>
-    <row r="4" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+    <row r="4" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A4" s="102"/>
       <c r="B4" s="93"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="117"/>
+      <c r="C4" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="117">
+        <v>1200</v>
+      </c>
       <c r="E4" s="105"/>
-      <c r="F4" s="96"/>
+      <c r="F4" s="96">
+        <v>373</v>
+      </c>
       <c r="G4" s="99">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(D4*F4)</f>
+        <v>447600</v>
       </c>
       <c r="H4" s="106"/>
     </row>
-    <row r="5" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+    <row r="5" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A5" s="102"/>
       <c r="B5" s="93"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="117"/>
+      <c r="C5" s="116" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="117">
+        <v>1200</v>
+      </c>
       <c r="E5" s="105"/>
-      <c r="F5" s="96"/>
+      <c r="F5" s="96">
+        <v>1100</v>
+      </c>
       <c r="G5" s="99">
-        <f t="shared" si="0"/>
+        <f>SUM(D5*F5)</f>
+        <v>1320000</v>
+      </c>
+      <c r="H5" s="106"/>
+    </row>
+    <row r="6" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A6" s="100"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99">
+        <f>SUM(D6*F6)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="106"/>
-    </row>
-    <row r="6" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
-      <c r="A6" s="102"/>
-      <c r="B6" s="93"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="99">
-        <f t="shared" si="0"/>
+      <c r="H6" s="99">
+        <f>SUM(G6:G9)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="106"/>
-    </row>
-    <row r="7" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+    </row>
+    <row r="7" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
       <c r="A7" s="102"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="118"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
       <c r="E7" s="105"/>
-      <c r="F7" s="96"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="99">
-        <f t="shared" si="0"/>
+        <f>SUM(D7*F7)</f>
         <v>0</v>
       </c>
       <c r="H7" s="106"/>
     </row>
-    <row r="8" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+    <row r="8" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
       <c r="A8" s="102"/>
-      <c r="B8" s="93"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="117"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
       <c r="E8" s="105"/>
-      <c r="F8" s="96"/>
+      <c r="F8" s="118"/>
       <c r="G8" s="99">
-        <f t="shared" si="0"/>
+        <f>SUM(D8*F8)</f>
         <v>0</v>
       </c>
       <c r="H8" s="106"/>
     </row>
-    <row r="9" s="87" customFormat="1" ht="32.15" customHeight="1" spans="1:8">
+    <row r="9" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
       <c r="A9" s="102"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="109"/>
-      <c r="F9" s="96"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="118"/>
       <c r="G9" s="99">
-        <f t="shared" si="0"/>
+        <f>SUM(D9*F9)</f>
         <v>0</v>
       </c>
       <c r="H9" s="106"/>
     </row>
-    <row r="10" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99">
-        <f t="shared" si="0"/>
+    <row r="10" s="87" customFormat="1" ht="258" customHeight="1" spans="1:8">
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="96">
+        <f>SUM(D10*F10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="99">
-        <f>SUM(G10:G13)</f>
+      <c r="H10" s="96">
+        <f>SUM(G10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A11" s="102"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="99">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="106"/>
-    </row>
-    <row r="12" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A12" s="102"/>
-      <c r="B12" s="103"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="99">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="106"/>
-    </row>
-    <row r="13" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A13" s="102"/>
-      <c r="B13" s="103"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="99">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="106"/>
-    </row>
-    <row r="14" s="87" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A14" s="92"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="96">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="96">
-        <f>SUM(G14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="87" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A15" s="123" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="124"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="129">
-        <f>SUM(H2:H14)</f>
-        <v>0</v>
+    <row r="11" s="87" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="A11" s="120" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="121"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="126">
+        <f>SUM(H2:H10)</f>
+        <v>4047600</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E2:E9"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="H2:H9"/>
-    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="H6:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2139,7 +2147,7 @@
         <v>221</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" s="94">
         <v>3</v>
@@ -2168,7 +2176,7 @@
         <v>254</v>
       </c>
       <c r="C3" s="98" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="94">
         <v>5</v>
@@ -2197,7 +2205,7 @@
         <v>523</v>
       </c>
       <c r="C4" s="98" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D4" s="94">
         <v>200</v>
@@ -2222,7 +2230,7 @@
       <c r="A5" s="102"/>
       <c r="B5" s="103"/>
       <c r="C5" s="98" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="104">
         <v>250</v>
@@ -2241,7 +2249,7 @@
       <c r="A6" s="107"/>
       <c r="B6" s="108"/>
       <c r="C6" s="98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D6" s="104">
         <v>150</v>
@@ -2335,10 +2343,10 @@
         <v>45968</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" s="54">
         <v>40</v>
@@ -2367,7 +2375,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="52"/>
       <c r="B4" s="61" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="62"/>
@@ -2381,7 +2389,7 @@
     <row r="5" spans="1:7">
       <c r="A5" s="52"/>
       <c r="B5" s="61" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="62"/>
@@ -2395,7 +2403,7 @@
     <row r="6" spans="1:7">
       <c r="A6" s="52"/>
       <c r="B6" s="61" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6" s="61"/>
       <c r="D6" s="62"/>
@@ -2439,7 +2447,7 @@
     <row r="10" spans="1:7">
       <c r="A10" s="72"/>
       <c r="B10" s="61" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C10" s="61"/>
       <c r="D10" s="62"/>
@@ -2453,7 +2461,7 @@
     <row r="11" spans="1:7">
       <c r="A11" s="74"/>
       <c r="B11" s="75" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C11" s="76"/>
       <c r="D11" s="62"/>
@@ -2464,7 +2472,7 @@
     <row r="12" spans="1:7">
       <c r="A12" s="72"/>
       <c r="B12" s="61" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="62"/>
@@ -2488,7 +2496,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="81" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14" s="82"/>
       <c r="C14" s="82"/>
@@ -2556,7 +2564,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
@@ -2812,10 +2820,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>4</v>
@@ -2835,7 +2843,7 @@
         <v>45982</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" s="18">
         <v>2</v>
@@ -2894,7 +2902,7 @@
     </row>
     <row r="7" s="12" customFormat="1" ht="39" customHeight="1" spans="1:7">
       <c r="A7" s="23" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" s="33"/>
       <c r="C7" s="33"/>
@@ -2930,13 +2938,13 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2944,11 +2952,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C2" s="8">
-        <f>'Anugrah (Bag, Cup, Box)'!H15</f>
-        <v>0</v>
+        <f>'Anugrah (Bag, Cup, Box)'!H11</f>
+        <v>4047600</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2956,7 +2964,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8">
         <f>'UD Abdi Jaya (Bag, Cup, Box)'!H8</f>
@@ -2968,7 +2976,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" s="8">
         <f>'PT. SUPARMA JAYA TBK (Tissue)'!E14</f>
@@ -2980,7 +2988,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" s="9">
         <f>'Vickel Laundry'!C32</f>
@@ -2992,7 +3000,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C6" s="9">
         <f>'Dishy Soap'!G7</f>
@@ -3006,7 +3014,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="10">
         <f>SUM(C2:C5)</f>
-        <v>1834482</v>
+        <v>5882082</v>
       </c>
     </row>
   </sheetData>

--- a/NOVEMBER/NOVEMBER FLOOR.xlsx
+++ b/NOVEMBER/NOVEMBER FLOOR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowWidth="19635" windowHeight="7500" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -32,168 +32,11 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_2900A6598AF34EAF8E34FD7992770F9A" descr="WhatsApp Image 2025-11-08 at 15.02.04_a7f4447b"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="2238" t="9976" b="14875"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5074920" y="374015"/>
-          <a:ext cx="2487295" cy="3405505"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_77CE357CEE334F6D961BD6780F917C7B" descr="WhatsApp Image 2025-11-17 at 19.55.24_b4d82a76"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect l="2094" t="17062" b="13764"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="7059930" y="-55880"/>
-          <a:ext cx="3651885" cy="4540885"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_53A5575CEC60468792705E317509501C" descr="WhatsApp Image 2025-11-17 at 19.55.38_dd252dd0"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:srcRect l="877" t="19263" b="10630"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="7574915" y="3136900"/>
-          <a:ext cx="3300730" cy="4071620"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="ID_65B137B176664CF88877812A0DB613B1" descr="WhatsApp Image 2025-11-24 at 18.54.44_1c844742"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:srcRect l="842" t="17045" r="2783" b="4116"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="6950710" y="-20955"/>
-          <a:ext cx="2959735" cy="4260215"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="ID_0EC8FE7F2FDE486BA9DB2B935A916937" descr="WhatsApp Image 2025-11-25 at 10.50.39_ab457d84"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:srcRect l="1551" t="17216" b="12348"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="7005320" y="9714865"/>
-          <a:ext cx="3377565" cy="4250055"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_1BF8DA62F9C54E9D82DEA162EB6C0D2C" descr="WhatsApp Image 2025-11-27 at 12.24.53_64d6a880"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:srcRect t="14478" r="1369" b="8928"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172835" y="573405"/>
-          <a:ext cx="2483485" cy="3385185"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
   <si>
     <t>DATE</t>
   </si>
@@ -265,6 +108,63 @@
   </si>
   <si>
     <t>STATUS</t>
+  </si>
+  <si>
+    <t>0395</t>
+  </si>
+  <si>
+    <t>0397</t>
+  </si>
+  <si>
+    <t>0398</t>
+  </si>
+  <si>
+    <t>0399</t>
+  </si>
+  <si>
+    <t>0400</t>
+  </si>
+  <si>
+    <t>0396</t>
+  </si>
+  <si>
+    <t>0870</t>
+  </si>
+  <si>
+    <t>0871</t>
+  </si>
+  <si>
+    <t>0872</t>
+  </si>
+  <si>
+    <t>0873</t>
+  </si>
+  <si>
+    <t>0874</t>
+  </si>
+  <si>
+    <t>0875</t>
+  </si>
+  <si>
+    <t>0880</t>
+  </si>
+  <si>
+    <t>0881</t>
+  </si>
+  <si>
+    <t>0882</t>
+  </si>
+  <si>
+    <t>0883</t>
+  </si>
+  <si>
+    <t>0885</t>
+  </si>
+  <si>
+    <t>0886</t>
+  </si>
+  <si>
+    <t>0887</t>
   </si>
   <si>
     <t>DESCRIPTION</t>
@@ -1547,6 +1447,9 @@
     <xf numFmtId="178" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1606,6 +1509,1006 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>42545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2200275</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>723900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_1BF8DA62F9C54E9D82DEA162EB6C0D2C" descr="WhatsApp Image 2025-11-27 at 12.24.53_64d6a880"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect t="14478" r="1369" b="8928"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5899785" y="245745"/>
+          <a:ext cx="2177415" cy="2967355"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>27305</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>27305</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3903345</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3143885</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_77CE357CEE334F6D961BD6780F917C7B" descr="WhatsApp Image 2025-11-17 at 19.55.24_b4d82a76"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect l="2094" t="17062" b="13764"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6819900" y="-149225"/>
+          <a:ext cx="3116580" cy="3876040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>26035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3898900</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>3160395</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_53A5575CEC60468792705E317509501C" descr="WhatsApp Image 2025-11-17 at 19.55.38_dd252dd0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect l="877" t="19263" b="10630"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6811010" y="3029585"/>
+          <a:ext cx="3134360" cy="3867150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>41275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3905250</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1016000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_0EC8FE7F2FDE486BA9DB2B935A916937" descr="WhatsApp Image 2025-11-25 at 10.50.39_ab457d84"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:srcRect l="1551" t="17216" b="12348"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6837045" y="6205220"/>
+          <a:ext cx="3082925" cy="3879215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>24765</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2289810</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1552575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_2900A6598AF34EAF8E34FD7992770F9A" descr="WhatsApp Image 2025-11-08 at 15.02.04_a7f4447b"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect l="2238" t="9976" b="14875"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4958715" y="222250"/>
+          <a:ext cx="2265045" cy="3101975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2392680</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3326130</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="ID_A61D43BAA8D944EE8EA75C5F0A349F33" descr="WhatsApp Image 2025-12-01 at 22.54.15_8a3b0306"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect t="3910" r="6347" b="22828"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567815" y="261620"/>
+          <a:ext cx="2369820" cy="3305810"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>20955</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2395220</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>3225165</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="ID_1F183DC8F48146A5B7AEB98446E6A11E" descr="WhatsApp Image 2025-12-01 at 22.54.37_aede8f40"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect t="4406" r="4082" b="23140"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1565910" y="3609975"/>
+          <a:ext cx="2374265" cy="3204845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>21590</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2394585</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3157855</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="ID_9455226B4250439A8E02C1CB0F10A6FA" descr="WhatsApp Image 2025-12-01 at 22.54.53_7b49f373"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:srcRect t="7993" r="2225" b="19669"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1566545" y="6849745"/>
+          <a:ext cx="2372995" cy="3137535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>21590</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393950</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>3236595</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="ID_50D05BE723D64CEA8CCEE9FE984866FA" descr="WhatsApp Image 2025-12-01 at 22.55.09_f0a8828e"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:srcRect l="2657" t="8928" r="5447" b="21427"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1566545" y="10024110"/>
+          <a:ext cx="2372360" cy="3216275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2392680</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>3202940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="ID_D906434F04FD4981A88A1F350F43C63B" descr="WhatsApp Image 2025-12-01 at 22.55.23_97f81f6f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:srcRect l="2404" t="9343" r="8302" b="23468"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567815" y="13278485"/>
+          <a:ext cx="2369820" cy="3182620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>20955</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393315</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3214370</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="ID_369F8EECD8E54694BAB777D05A717FB1" descr="WhatsApp Image 2025-12-01 at 22.55.38_4dcf6c65"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:srcRect l="1259" t="9203" r="4350" b="19553"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567815" y="16503015"/>
+          <a:ext cx="2370455" cy="3193415"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>21590</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393950</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>3225165</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="ID_6FDC72CF0C4B432DB010F77E0415D702" descr="WhatsApp Image 2025-12-01 at 22.55.52_4696b50e"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:srcRect l="2955" t="10284" r="8194" b="22481"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1566545" y="19736435"/>
+          <a:ext cx="2372360" cy="3204845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393950</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>3370580</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="ID_B4289229848240F7B60BD1765A7C3FD8" descr="WhatsApp Image 2025-12-01 at 22.56.18_c856e6d6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:srcRect t="8513" r="7291" b="18060"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567180" y="22979380"/>
+          <a:ext cx="2371725" cy="3350260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>20320</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>21590</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2395855</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3314065</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="ID_6AE55F3D6342489CA976AE9EB1CEAA3D" descr="WhatsApp Image 2025-12-01 at 22.56.42_798139f6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:srcRect l="3406" t="7310" r="3630" b="20512"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1565275" y="26370915"/>
+          <a:ext cx="2375535" cy="3292475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>20320</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2395855</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3313430</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="ID_D79BA9A2D3C0489BBBACB22648D9F53A" descr="WhatsApp Image 2025-12-01 at 22.56.55_adf37c6e"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:srcRect l="3394" t="10553" r="4834" b="18300"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1565275" y="29698315"/>
+          <a:ext cx="2375535" cy="3291205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2392680</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3415665</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="ID_D3E4FF05D869452992B7F4CB31EF54D5" descr="WhatsApp Image 2025-12-01 at 23.02.55_c9cb98b3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:srcRect t="7864" b="11922"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567815" y="33022540"/>
+          <a:ext cx="2369820" cy="3395345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>20320</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>20955</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2395855</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3302000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="ID_3777388570C947DAB56AF29997CAE53B" descr="WhatsApp Image 2025-12-01 at 23.03.33_12f060bf"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:srcRect l="2934" t="8655" r="5532" b="20451"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1565275" y="36461065"/>
+          <a:ext cx="2375535" cy="3281045"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>21590</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393950</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>3248025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="ID_A12157C6793548E988BC95ECA6ECD63A" descr="WhatsApp Image 2025-12-01 at 23.03.48_23ec04eb"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:srcRect t="9342" r="6089" b="19046"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1566545" y="39776400"/>
+          <a:ext cx="2372360" cy="3227705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2392680</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3326130</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="ID_9FEFCB772F734B0888981ADF44925CB6" descr="WhatsApp Image 2025-12-01 at 23.04.38_10fca869"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:srcRect l="4349" t="10417" r="5585" b="19236"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567815" y="43042205"/>
+          <a:ext cx="2369820" cy="3305810"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>21590</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2394585</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3415665</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="ID_EBEADDDF93A340A3BCD9593D5CDFE517" descr="WhatsApp Image 2025-12-01 at 23.05.01_f7794176"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:srcRect l="5562" t="9468" r="6057" b="19681"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1566545" y="46389290"/>
+          <a:ext cx="2372995" cy="3395345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393315</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3303905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="ID_358536F7AFE24460BCFE4DF1CE0D61C0" descr="WhatsApp Image 2025-12-01 at 23.06.11_30a9c7d7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:srcRect t="9749" r="7209" b="18433"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567180" y="49822735"/>
+          <a:ext cx="2371090" cy="3283585"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393315</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>3281045</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="ID_14133977134C4721B96185F203920983" descr="WhatsApp Image 2025-12-01 at 23.04.14_15c00130"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:srcRect t="10417" r="6015" b="17204"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567815" y="53146325"/>
+          <a:ext cx="2370455" cy="3260725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>20955</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2394585</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3326130</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="ID_6100CF163CFF48C5BCA732685D815AD2" descr="WhatsApp Image 2025-12-01 at 23.06.33_26fd94b2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:srcRect l="4595" t="10416" r="6561" b="20227"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1565910" y="56448325"/>
+          <a:ext cx="2373630" cy="3305810"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2393950</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>3662045</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="ID_21A96F554346403BBA012A2A4B7A84C2" descr="WhatsApp Image 2025-12-01 at 23.06.50_ffebf2f1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:srcRect l="5316" t="5278" r="6755" b="19104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1567180" y="59790965"/>
+          <a:ext cx="2371725" cy="3641725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>45085</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4321175</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3004820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="ID_65B137B176664CF88877812A0DB613B1" descr="WhatsApp Image 2025-11-24 at 18.54.44_1c844742"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect l="842" t="17045" r="2783" b="4116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6009640" y="-160655"/>
+          <a:ext cx="2959735" cy="4260215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1920,15 +2823,12 @@
       <c r="D2" s="117">
         <v>400</v>
       </c>
-      <c r="E2" s="95" t="str">
-        <f>_xlfn.DISPIMG("ID_1BF8DA62F9C54E9D82DEA162EB6C0D2C",1)</f>
-        <v>=DISPIMG("ID_1BF8DA62F9C54E9D82DEA162EB6C0D2C",1)</v>
-      </c>
+      <c r="E2" s="95"/>
       <c r="F2" s="96">
         <v>2900</v>
       </c>
       <c r="G2" s="99">
-        <f>SUM(D2*F2)</f>
+        <f t="shared" ref="G2:G10" si="0">SUM(D2*F2)</f>
         <v>1160000</v>
       </c>
       <c r="H2" s="99">
@@ -1950,7 +2850,7 @@
         <v>2800</v>
       </c>
       <c r="G3" s="99">
-        <f>SUM(D3*F3)</f>
+        <f t="shared" si="0"/>
         <v>1120000</v>
       </c>
       <c r="H3" s="106"/>
@@ -1969,7 +2869,7 @@
         <v>373</v>
       </c>
       <c r="G4" s="99">
-        <f>SUM(D4*F4)</f>
+        <f t="shared" si="0"/>
         <v>447600</v>
       </c>
       <c r="H4" s="106"/>
@@ -1988,7 +2888,7 @@
         <v>1100</v>
       </c>
       <c r="G5" s="99">
-        <f>SUM(D5*F5)</f>
+        <f t="shared" si="0"/>
         <v>1320000</v>
       </c>
       <c r="H5" s="106"/>
@@ -2001,7 +2901,7 @@
       <c r="E6" s="95"/>
       <c r="F6" s="99"/>
       <c r="G6" s="99">
-        <f>SUM(D6*F6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6" s="99">
@@ -2017,7 +2917,7 @@
       <c r="E7" s="105"/>
       <c r="F7" s="118"/>
       <c r="G7" s="99">
-        <f>SUM(D7*F7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7" s="106"/>
@@ -2030,7 +2930,7 @@
       <c r="E8" s="105"/>
       <c r="F8" s="118"/>
       <c r="G8" s="99">
-        <f>SUM(D8*F8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H8" s="106"/>
@@ -2043,7 +2943,7 @@
       <c r="E9" s="105"/>
       <c r="F9" s="118"/>
       <c r="G9" s="99">
-        <f>SUM(D9*F9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H9" s="106"/>
@@ -2056,7 +2956,7 @@
       <c r="E10" s="111"/>
       <c r="F10" s="119"/>
       <c r="G10" s="96">
-        <f>SUM(D10*F10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H10" s="96">
@@ -2093,6 +2993,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2139,7 +3040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="87" customFormat="1" ht="249.35" spans="1:8">
+    <row r="2" s="87" customFormat="1" ht="249.35" customHeight="1" spans="1:8">
       <c r="A2" s="92">
         <v>45975</v>
       </c>
@@ -2152,10 +3053,7 @@
       <c r="D2" s="94">
         <v>3</v>
       </c>
-      <c r="E2" s="95" t="str">
-        <f>_xlfn.DISPIMG("ID_77CE357CEE334F6D961BD6780F917C7B",1)</f>
-        <v>=DISPIMG("ID_77CE357CEE334F6D961BD6780F917C7B",1)</v>
-      </c>
+      <c r="E2" s="95"/>
       <c r="F2" s="96">
         <v>55000</v>
       </c>
@@ -2168,7 +3066,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="3" s="87" customFormat="1" ht="251.35" spans="1:8">
+    <row r="3" s="87" customFormat="1" ht="251.35" customHeight="1" spans="1:8">
       <c r="A3" s="92">
         <v>45976</v>
       </c>
@@ -2181,10 +3079,7 @@
       <c r="D3" s="94">
         <v>5</v>
       </c>
-      <c r="E3" s="95" t="str">
-        <f>_xlfn.DISPIMG("ID_53A5575CEC60468792705E317509501C",1)</f>
-        <v>=DISPIMG("ID_53A5575CEC60468792705E317509501C",1)</v>
-      </c>
+      <c r="E3" s="95"/>
       <c r="F3" s="97">
         <v>13000</v>
       </c>
@@ -2210,10 +3105,7 @@
       <c r="D4" s="94">
         <v>200</v>
       </c>
-      <c r="E4" s="95" t="str">
-        <f>_xlfn.DISPIMG("ID_0EC8FE7F2FDE486BA9DB2B935A916937",1)</f>
-        <v>=DISPIMG("ID_0EC8FE7F2FDE486BA9DB2B935A916937",1)</v>
-      </c>
+      <c r="E4" s="95"/>
       <c r="F4" s="97">
         <v>2300</v>
       </c>
@@ -2297,6 +3189,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2351,10 +3244,7 @@
       <c r="D2" s="54">
         <v>40</v>
       </c>
-      <c r="E2" s="55" t="str">
-        <f>_xlfn.DISPIMG("ID_2900A6598AF34EAF8E34FD7992770F9A",1)</f>
-        <v>=DISPIMG("ID_2900A6598AF34EAF8E34FD7992770F9A",1)</v>
-      </c>
+      <c r="E2" s="55"/>
       <c r="F2" s="56">
         <v>6063.96</v>
       </c>
@@ -2533,6 +3423,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2542,9 +3433,9 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" style="12"/>
+    <col min="1" max="1" width="10.5714285714286" style="12" customWidth="1"/>
     <col min="2" max="2" width="12.6" style="36" customWidth="1"/>
-    <col min="3" max="3" width="38.7142857142857" style="12" customWidth="1"/>
+    <col min="3" max="3" width="36.1238095238095" style="12" customWidth="1"/>
     <col min="4" max="4" width="18.8285714285714" style="12" customWidth="1"/>
     <col min="5" max="5" width="12.2857142857143" style="12" customWidth="1"/>
     <col min="6" max="16384" width="9.14285714285714" style="12"/>
@@ -2567,137 +3458,251 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
+    <row r="2" s="12" customFormat="1" ht="263.65" customHeight="1" spans="1:5">
+      <c r="A2" s="39">
+        <v>45962</v>
+      </c>
+      <c r="B2" s="127" t="s">
+        <v>24</v>
+      </c>
       <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
+      <c r="D2" s="42">
+        <v>72000</v>
+      </c>
       <c r="E2" s="41"/>
     </row>
-    <row r="3" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
+    <row r="3" s="12" customFormat="1" ht="255.1" customHeight="1" spans="1:5">
+      <c r="A3" s="39">
+        <v>45964</v>
+      </c>
+      <c r="B3" s="127" t="s">
+        <v>25</v>
+      </c>
       <c r="C3" s="41"/>
-      <c r="D3" s="43"/>
+      <c r="D3" s="43">
+        <v>16000</v>
+      </c>
       <c r="E3" s="44"/>
     </row>
-    <row r="4" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
+    <row r="4" s="12" customFormat="1" ht="249.95" customHeight="1" spans="1:5">
+      <c r="A4" s="39">
+        <v>45965</v>
+      </c>
+      <c r="B4" s="127" t="s">
+        <v>26</v>
+      </c>
       <c r="C4" s="41"/>
-      <c r="D4" s="43"/>
+      <c r="D4" s="43">
+        <v>80000</v>
+      </c>
       <c r="E4" s="44"/>
     </row>
-    <row r="5" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A5" s="39"/>
-      <c r="B5" s="40"/>
+    <row r="5" s="12" customFormat="1" ht="256.25" customHeight="1" spans="1:5">
+      <c r="A5" s="39">
+        <v>45966</v>
+      </c>
+      <c r="B5" s="127" t="s">
+        <v>27</v>
+      </c>
       <c r="C5" s="41"/>
-      <c r="D5" s="43"/>
+      <c r="D5" s="43">
+        <v>16000</v>
+      </c>
       <c r="E5" s="44"/>
     </row>
-    <row r="6" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A6" s="39"/>
-      <c r="B6" s="40"/>
+    <row r="6" s="12" customFormat="1" ht="253.85" customHeight="1" spans="1:5">
+      <c r="A6" s="39">
+        <v>45967</v>
+      </c>
+      <c r="B6" s="127" t="s">
+        <v>28</v>
+      </c>
       <c r="C6" s="41"/>
-      <c r="D6" s="43"/>
+      <c r="D6" s="43">
+        <v>63000</v>
+      </c>
       <c r="E6" s="44"/>
     </row>
-    <row r="7" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
+    <row r="7" s="12" customFormat="1" ht="254.65" customHeight="1" spans="1:5">
+      <c r="A7" s="39">
+        <v>45968</v>
+      </c>
+      <c r="B7" s="127" t="s">
+        <v>29</v>
+      </c>
       <c r="C7" s="41"/>
-      <c r="D7" s="43"/>
+      <c r="D7" s="43">
+        <v>48000</v>
+      </c>
       <c r="E7" s="44"/>
     </row>
-    <row r="8" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A8" s="39"/>
-      <c r="B8" s="40"/>
+    <row r="8" s="12" customFormat="1" ht="255.35" customHeight="1" spans="1:5">
+      <c r="A8" s="39">
+        <v>45969</v>
+      </c>
+      <c r="B8" s="127" t="s">
+        <v>30</v>
+      </c>
       <c r="C8" s="41"/>
-      <c r="D8" s="43"/>
+      <c r="D8" s="43">
+        <v>16000</v>
+      </c>
       <c r="E8" s="44"/>
     </row>
-    <row r="9" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40"/>
+    <row r="9" s="12" customFormat="1" ht="266.95" customHeight="1" spans="1:5">
+      <c r="A9" s="39">
+        <v>45971</v>
+      </c>
+      <c r="B9" s="127" t="s">
+        <v>31</v>
+      </c>
       <c r="C9" s="41"/>
-      <c r="D9" s="43"/>
+      <c r="D9" s="43">
+        <v>80000</v>
+      </c>
       <c r="E9" s="44"/>
     </row>
-    <row r="10" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
+    <row r="10" s="12" customFormat="1" ht="261.95" customHeight="1" spans="1:5">
+      <c r="A10" s="39">
+        <v>45972</v>
+      </c>
+      <c r="B10" s="127" t="s">
+        <v>32</v>
+      </c>
       <c r="C10" s="41"/>
-      <c r="D10" s="43"/>
+      <c r="D10" s="43">
+        <v>24000</v>
+      </c>
       <c r="E10" s="44"/>
     </row>
-    <row r="11" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
+    <row r="11" s="12" customFormat="1" ht="261.9" customHeight="1" spans="1:5">
+      <c r="A11" s="39">
+        <v>45973</v>
+      </c>
+      <c r="B11" s="127" t="s">
+        <v>33</v>
+      </c>
       <c r="C11" s="41"/>
-      <c r="D11" s="43"/>
+      <c r="D11" s="43">
+        <v>24000</v>
+      </c>
       <c r="E11" s="44"/>
     </row>
-    <row r="12" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
+    <row r="12" s="12" customFormat="1" ht="270.7" customHeight="1" spans="1:5">
+      <c r="A12" s="39">
+        <v>45976</v>
+      </c>
+      <c r="B12" s="127" t="s">
+        <v>34</v>
+      </c>
       <c r="C12" s="41"/>
-      <c r="D12" s="43"/>
+      <c r="D12" s="43">
+        <v>96000</v>
+      </c>
       <c r="E12" s="44"/>
     </row>
-    <row r="13" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
+    <row r="13" s="12" customFormat="1" ht="261.1" customHeight="1" spans="1:5">
+      <c r="A13" s="39">
+        <v>45977</v>
+      </c>
+      <c r="B13" s="127" t="s">
+        <v>35</v>
+      </c>
       <c r="C13" s="41"/>
-      <c r="D13" s="43"/>
+      <c r="D13" s="43">
+        <v>32000</v>
+      </c>
       <c r="E13" s="44"/>
     </row>
-    <row r="14" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
+    <row r="14" s="12" customFormat="1" ht="257.15" customHeight="1" spans="1:5">
+      <c r="A14" s="39">
+        <v>45980</v>
+      </c>
+      <c r="B14" s="127" t="s">
+        <v>36</v>
+      </c>
       <c r="C14" s="41"/>
-      <c r="D14" s="43"/>
+      <c r="D14" s="43">
+        <v>24000</v>
+      </c>
       <c r="E14" s="44"/>
     </row>
-    <row r="15" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
+    <row r="15" s="12" customFormat="1" ht="263.55" customHeight="1" spans="1:5">
+      <c r="A15" s="39">
+        <v>45982</v>
+      </c>
+      <c r="B15" s="127" t="s">
+        <v>37</v>
+      </c>
       <c r="C15" s="41"/>
-      <c r="D15" s="43"/>
+      <c r="D15" s="43">
+        <v>64000</v>
+      </c>
       <c r="E15" s="44"/>
     </row>
-    <row r="16" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
+    <row r="16" s="12" customFormat="1" ht="270.35" customHeight="1" spans="1:5">
+      <c r="A16" s="39">
+        <v>45983</v>
+      </c>
+      <c r="B16" s="127" t="s">
+        <v>38</v>
+      </c>
       <c r="C16" s="41"/>
-      <c r="D16" s="43"/>
+      <c r="D16" s="43">
+        <v>40000</v>
+      </c>
       <c r="E16" s="44"/>
     </row>
-    <row r="17" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
+    <row r="17" s="12" customFormat="1" ht="261.7" customHeight="1" spans="1:5">
+      <c r="A17" s="39">
+        <v>45984</v>
+      </c>
+      <c r="B17" s="127" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="41"/>
-      <c r="D17" s="43"/>
+      <c r="D17" s="43">
+        <v>24000</v>
+      </c>
       <c r="E17" s="44"/>
     </row>
-    <row r="18" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A18" s="39"/>
-      <c r="B18" s="40"/>
+    <row r="18" s="12" customFormat="1" ht="260" customHeight="1" spans="1:5">
+      <c r="A18" s="39">
+        <v>45985</v>
+      </c>
+      <c r="B18" s="127" t="s">
+        <v>40</v>
+      </c>
       <c r="C18" s="41"/>
-      <c r="D18" s="43"/>
+      <c r="D18" s="43">
+        <v>48000</v>
+      </c>
       <c r="E18" s="44"/>
     </row>
-    <row r="19" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A19" s="39"/>
-      <c r="B19" s="40"/>
+    <row r="19" s="12" customFormat="1" ht="263.2" customHeight="1" spans="1:5">
+      <c r="A19" s="39">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="127" t="s">
+        <v>41</v>
+      </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="43"/>
+      <c r="D19" s="43">
+        <v>16000</v>
+      </c>
       <c r="E19" s="44"/>
     </row>
-    <row r="20" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
+    <row r="20" s="12" customFormat="1" ht="289.95" customHeight="1" spans="1:5">
+      <c r="A20" s="39">
+        <v>45989</v>
+      </c>
+      <c r="B20" s="127" t="s">
+        <v>42</v>
+      </c>
       <c r="C20" s="41"/>
-      <c r="D20" s="43"/>
+      <c r="D20" s="43">
+        <v>64000</v>
+      </c>
       <c r="E20" s="44"/>
     </row>
     <row r="21" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
@@ -2786,7 +3791,7 @@
       <c r="B32" s="46"/>
       <c r="C32" s="47">
         <f>SUM(D2:D31)</f>
-        <v>0</v>
+        <v>847000</v>
       </c>
       <c r="D32" s="48"/>
       <c r="E32" s="49"/>
@@ -2798,6 +3803,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2820,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>4</v>
@@ -2838,20 +3844,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" ht="240.3" spans="1:7">
+    <row r="2" s="12" customFormat="1" ht="240.3" customHeight="1" spans="1:7">
       <c r="A2" s="16">
         <v>45982</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C2" s="18">
         <v>2</v>
       </c>
-      <c r="D2" s="19" t="str">
-        <f>_xlfn.DISPIMG("ID_65B137B176664CF88877812A0DB613B1",1)</f>
-        <v>=DISPIMG("ID_65B137B176664CF88877812A0DB613B1",1)</v>
-      </c>
+      <c r="D2" s="19"/>
       <c r="E2" s="20">
         <v>55000</v>
       </c>
@@ -2922,6 +3925,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2938,13 +3942,13 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2952,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C2" s="8">
         <f>'Anugrah (Bag, Cup, Box)'!H11</f>
@@ -2964,7 +3968,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C3" s="8">
         <f>'UD Abdi Jaya (Bag, Cup, Box)'!H8</f>
@@ -2976,7 +3980,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C4" s="8">
         <f>'PT. SUPARMA JAYA TBK (Tissue)'!E14</f>
@@ -2988,11 +3992,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C5" s="9">
         <f>'Vickel Laundry'!C32</f>
-        <v>0</v>
+        <v>847000</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3000,7 +4004,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C6" s="9">
         <f>'Dishy Soap'!G7</f>
@@ -3014,7 +4018,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="10">
         <f>SUM(C2:C5)</f>
-        <v>5882082</v>
+        <v>6729082</v>
       </c>
     </row>
   </sheetData>

--- a/NOVEMBER/NOVEMBER FLOOR.xlsx
+++ b/NOVEMBER/NOVEMBER FLOOR.xlsx
@@ -29,10 +29,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3913,7 +3909,7 @@
       <c r="E7" s="33"/>
       <c r="F7" s="28"/>
       <c r="G7" s="34">
-        <f>SUM(G2)</f>
+        <f>SUM(G2:G6)</f>
         <v>110000</v>
       </c>
     </row>
